--- a/test-case-exports/Reconciliation.xlsx
+++ b/test-case-exports/Reconciliation.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -62,7 +62,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Castlemock (EMI→ANB mock) + EOD job endpoint access (EMI-636/637/710/5258)</t>
+    <t>Skipped: pending Castlemock (EMI→ANB mock) + EOD job endpoint access (EMI-636/637/710/5258)</t>
   </si>
   <si>
     <t>EOD-02: EOD external reconciliation with ANB reconciles bank records against system transactions (EMI-637)</t>
@@ -128,7 +128,7 @@
     <t>RC-01: importing a bank statement flags a transaction missing from the system</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal / Reconciliation Ops tooling access (EMI-4537/EMI-2177)</t>
+    <t>Skipped: pending Admin Portal / Reconciliation Ops tooling access (EMI-4537/EMI-2177)</t>
   </si>
   <si>
     <t>RC-02: importing a bank statement flags an amount/status/date discrepancy</t>
@@ -200,13 +200,13 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.348Z</t>
+    <t>2026-09-08T15:08:53.615Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>api</t>
@@ -221,7 +221,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -239,6 +242,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -248,7 +252,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,11 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -280,8 +279,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -626,16 +629,18 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,36 +669,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -722,36 +727,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -780,36 +785,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -838,36 +843,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -896,36 +901,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -954,36 +959,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1012,36 +1017,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1070,36 +1075,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1128,36 +1133,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1186,36 +1191,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1244,36 +1249,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1302,36 +1307,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1360,36 +1365,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1418,36 +1423,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1476,36 +1481,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1534,36 +1539,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1592,36 +1597,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1650,36 +1655,36 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" t="s">
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1708,37 +1713,37 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="G38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1746,16 +1751,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1774,11 +1790,21 @@
         <v>37</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1788,11 +1814,21 @@
         <v>37</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1818,11 +1854,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
     </row>
